--- a/docs/excel-book/projets/Projet4-Releve-de-notes.xlsx
+++ b/docs/excel-book/projets/Projet4-Releve-de-notes.xlsx
@@ -721,11 +721,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24233072"/>
-        <c:axId val="18233475"/>
+        <c:axId val="66010951"/>
+        <c:axId val="57379655"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24233072"/>
+        <c:axId val="66010951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -757,7 +757,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18233475"/>
+        <c:crossAx val="57379655"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -765,7 +765,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18233475"/>
+        <c:axId val="57379655"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -807,7 +807,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24233072"/>
+        <c:crossAx val="66010951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
